--- a/Data/Wind Power.xlsx
+++ b/Data/Wind Power.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AAAB3B-DF72-8D4B-BFBC-7BFCD43EB45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EC68F3-7E3D-9A44-824E-9CB53FB6B9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Initial values" sheetId="5" r:id="rId1"/>
-    <sheet name="Initial values seasonal" sheetId="1" r:id="rId2"/>
-    <sheet name="Advancements1" sheetId="2" r:id="rId3"/>
-    <sheet name="Extras1" sheetId="4" r:id="rId4"/>
-    <sheet name="Extras2" sheetId="6" r:id="rId5"/>
+    <sheet name="Initial values" sheetId="7" r:id="rId1"/>
+    <sheet name="Initial values hourly old" sheetId="5" r:id="rId2"/>
+    <sheet name="Initial values seasonal" sheetId="1" r:id="rId3"/>
+    <sheet name="Advancements1" sheetId="2" r:id="rId4"/>
+    <sheet name="Extras1" sheetId="4" r:id="rId5"/>
+    <sheet name="Extras2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="107">
   <si>
     <t>Metrics</t>
   </si>
@@ -352,6 +353,15 @@
   </si>
   <si>
     <t>Spatial requirement</t>
+  </si>
+  <si>
+    <t>Goldwind 165-6.0MW</t>
+  </si>
+  <si>
+    <t>Installation Cost 2024 USD</t>
+  </si>
+  <si>
+    <t>Spatial Requirement m^2</t>
   </si>
 </sst>
 </file>
@@ -4271,7 +4281,7 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>Extras1!$C$136:$C$150</c:f>
+              <c:f>Extras1!$C$139:$C$153</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
@@ -4593,7 +4603,7 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>Extras1!$C$136:$C$158</c:f>
+              <c:f>Extras1!$C$139:$C$161</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="23"/>
@@ -11021,7 +11031,7 @@
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>59069</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>133364</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11051,13 +11061,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>652720</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>149907</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>59069</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>148135</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11087,13 +11097,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>362238</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>129308</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>43295</xdr:colOff>
-      <xdr:row>149</xdr:row>
+      <xdr:row>152</xdr:row>
       <xdr:rowOff>43295</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11123,13 +11133,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>847132</xdr:colOff>
-      <xdr:row>151</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>107741</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>674077</xdr:colOff>
-      <xdr:row>164</xdr:row>
+      <xdr:row>167</xdr:row>
       <xdr:rowOff>129513</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11531,6 +11541,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690F904E-92CB-A441-A858-D728B93340E4}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5430435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>82435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <f>(1-0.67)/B4</f>
+        <v>1.3199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <f>B2*0.67</f>
+        <v>3638391.45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11">
+        <v>0.89800000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12">
+        <v>86409</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02F4A57-A2BE-384A-8025-E4A1F08C861C}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -11879,28 +12001,28 @@
         <v>94</v>
       </c>
       <c r="B12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="C12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="D12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="E12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="F12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="G12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="H12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="I12">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -11937,7 +12059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A33B43-D754-5346-B372-5334A6F317AF}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -12365,28 +12487,28 @@
         <v>94</v>
       </c>
       <c r="B15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="C15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="D15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="E15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="F15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="G15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="H15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="I15">
-        <v>0.89775450085911801</v>
+        <v>0.89800000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -12395,7 +12517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6734CF1-7336-B242-BB78-8AD8C045F5E6}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -12475,9 +12597,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6B8A3E-987F-534C-BE5F-E1607AAFBDBF}">
-  <dimension ref="A1:Y158"/>
+  <dimension ref="A1:Y161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
@@ -14363,981 +14485,1054 @@
         <v>246272</v>
       </c>
     </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81" t="s">
+        <v>30</v>
+      </c>
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>104</v>
+      </c>
+      <c r="B82">
+        <v>165.846</v>
+      </c>
+      <c r="C82">
+        <v>6000</v>
+      </c>
+      <c r="D82">
+        <v>3</v>
+      </c>
+      <c r="E82">
+        <v>11.4</v>
+      </c>
+      <c r="F82">
+        <v>24</v>
+      </c>
+      <c r="G82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>105</v>
+      </c>
+      <c r="B83">
+        <f>21721740/4</f>
+        <v>5430435</v>
+      </c>
+    </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D84" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
+      <c r="A84" t="s">
+        <v>78</v>
+      </c>
+      <c r="B84">
+        <f>$C$155*$L$100*C82</f>
+        <v>82435.502492885134</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>106</v>
+      </c>
+      <c r="B85">
+        <f>PI()*B82*B82</f>
+        <v>86409.17831913897</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D87" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>77</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B88" t="s">
         <v>80</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C88" t="s">
         <v>24</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D88" t="s">
         <v>49</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E88" t="s">
         <v>50</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F88" t="s">
         <v>51</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G88" t="s">
         <v>52</v>
       </c>
-      <c r="L85" t="s">
+      <c r="L88" t="s">
         <v>78</v>
       </c>
-      <c r="N85" t="s">
+      <c r="N88" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <f t="shared" ref="A86:A93" si="0">$C$117*B86/1000</f>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <f t="shared" ref="A89:A96" si="0">$C$120*B89/1000</f>
         <v>726928.47499999998</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B89" s="1">
         <v>910</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C89" t="s">
         <v>23</v>
       </c>
-      <c r="D86">
+      <c r="D89">
         <f>SUM(B5:D8)/4</f>
         <v>135756.625</v>
       </c>
-      <c r="E86">
+      <c r="E89">
         <f>SUM(E5:G8)/4</f>
         <v>101216.97500000001</v>
       </c>
-      <c r="F86">
+      <c r="F89">
         <f>SUM(H5:J8)/4</f>
         <v>101966.32499999998</v>
       </c>
-      <c r="G86">
+      <c r="G89">
         <f>SUM(K5:M8)/4</f>
         <v>81962.125</v>
       </c>
-      <c r="H86" t="str">
-        <f>_xlfn.TEXTJOIN(",", TRUE, D86, E86, F86, G86)</f>
+      <c r="H89" t="str">
+        <f>_xlfn.TEXTJOIN(",", TRUE, D89, E89, F89, G89)</f>
         <v>135756.625,101216.975,101966.325,81962.125</v>
       </c>
-      <c r="L86">
-        <f t="shared" ref="L86:L91" si="1">$C$152*$L$97*B86</f>
+      <c r="L89">
+        <f>$C$155*$L$100*B89</f>
         <v>12502.717878087578</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <f t="shared" si="0"/>
-        <v>1637586.125</v>
-      </c>
-      <c r="B87" s="1">
-        <v>2050</v>
-      </c>
-      <c r="C87" t="s">
-        <v>39</v>
-      </c>
-      <c r="D87">
-        <f>SUM(B15:D18)/4</f>
-        <v>603989.25</v>
-      </c>
-      <c r="E87">
-        <f>SUM(E15:G18)/4</f>
-        <v>461937.92500000005</v>
-      </c>
-      <c r="F87">
-        <f>SUM(H15:J18)/4</f>
-        <v>483683.25</v>
-      </c>
-      <c r="G87">
-        <f>SUM(K15:M18)/4</f>
-        <v>364889.02499999997</v>
-      </c>
-      <c r="H87" t="str">
-        <f t="shared" ref="H87:H93" si="2">_xlfn.TEXTJOIN(",", TRUE, D87, E87, F87, G87)</f>
-        <v>603989.25,461937.925,483683.25,364889.025</v>
-      </c>
-      <c r="L87">
-        <f t="shared" si="1"/>
-        <v>28165.463351735754</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <f t="shared" si="0"/>
-        <v>1845279.9750000001</v>
-      </c>
-      <c r="B88" s="1">
-        <v>2310</v>
-      </c>
-      <c r="C88" t="s">
-        <v>41</v>
-      </c>
-      <c r="D88">
-        <f>SUM(B25:D28)/4</f>
-        <v>472581.25</v>
-      </c>
-      <c r="E88">
-        <f>SUM(E25:G28)/4</f>
-        <v>354581.44999999995</v>
-      </c>
-      <c r="F88">
-        <f>SUM(H25:J28)/4</f>
-        <v>362762.25</v>
-      </c>
-      <c r="G88">
-        <f>SUM(K25:M28)/4</f>
-        <v>282265.57500000001</v>
-      </c>
-      <c r="H88" t="str">
-        <f t="shared" si="2"/>
-        <v>472581.25,354581.45,362762.25,282265.575</v>
-      </c>
-      <c r="L88">
-        <f t="shared" si="1"/>
-        <v>31737.668459760775</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <f t="shared" si="0"/>
-        <v>2396467.5</v>
-      </c>
-      <c r="B89" s="1">
-        <v>3000</v>
-      </c>
-      <c r="C89" t="s">
-        <v>43</v>
-      </c>
-      <c r="D89">
-        <f>SUM(B35:D38)/4</f>
-        <v>607253.75</v>
-      </c>
-      <c r="E89">
-        <f>SUM(E35:G38)/4</f>
-        <v>453880.02499999997</v>
-      </c>
-      <c r="F89">
-        <f>SUM(H35:J38)/4</f>
-        <v>468407</v>
-      </c>
-      <c r="G89">
-        <f>SUM(K35:M38)/4</f>
-        <v>360940.55</v>
-      </c>
-      <c r="H89" t="str">
-        <f t="shared" si="2"/>
-        <v>607253.75,453880.025,468407,360940.55</v>
-      </c>
-      <c r="L89">
-        <f t="shared" si="1"/>
-        <v>41217.751246442567</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <f t="shared" si="0"/>
-        <v>1318057.125</v>
+        <v>1637586.125</v>
       </c>
       <c r="B90" s="1">
-        <v>1650</v>
+        <v>2050</v>
       </c>
       <c r="C90" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D90">
-        <f>SUM(B45:D48)/4</f>
-        <v>641216</v>
+        <f>SUM(B15:D18)/4</f>
+        <v>603989.25</v>
       </c>
       <c r="E90">
-        <f>SUM(E45:G48)/4</f>
-        <v>507398.45</v>
+        <f>SUM(E15:G18)/4</f>
+        <v>461937.92500000005</v>
       </c>
       <c r="F90">
-        <f>SUM(H45:J48)/4</f>
-        <v>565767</v>
+        <f>SUM(H15:J18)/4</f>
+        <v>483683.25</v>
       </c>
       <c r="G90">
-        <f>SUM(K45:M48)/4</f>
-        <v>403365.80000000005</v>
+        <f>SUM(K15:M18)/4</f>
+        <v>364889.02499999997</v>
       </c>
       <c r="H90" t="str">
-        <f t="shared" si="2"/>
-        <v>641216,507398.45,565767,403365.8</v>
+        <f t="shared" ref="H90:H96" si="1">_xlfn.TEXTJOIN(",", TRUE, D90, E90, F90, G90)</f>
+        <v>603989.25,461937.925,483683.25,364889.025</v>
       </c>
       <c r="L90">
-        <f t="shared" si="1"/>
-        <v>22669.763185543412</v>
+        <f>$C$155*$L$100*B90</f>
+        <v>28165.463351735754</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <f t="shared" si="0"/>
-        <v>678999.125</v>
+        <v>1845279.9750000001</v>
       </c>
       <c r="B91" s="1">
-        <v>850</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>47</v>
+        <v>2310</v>
+      </c>
+      <c r="C91" t="s">
+        <v>41</v>
       </c>
       <c r="D91">
-        <f>SUM(B55:D58)/4</f>
-        <v>113092</v>
+        <f>SUM(B25:D28)/4</f>
+        <v>472581.25</v>
       </c>
       <c r="E91">
-        <f>SUM(E55:G58)/4</f>
-        <v>80781.349999999991</v>
+        <f>SUM(E25:G28)/4</f>
+        <v>354581.44999999995</v>
       </c>
       <c r="F91">
-        <f>SUM(H55:J58)/4</f>
-        <v>82349.649999999994</v>
+        <f>SUM(H25:J28)/4</f>
+        <v>362762.25</v>
       </c>
       <c r="G91">
-        <f>SUM(K55:M58)/4</f>
-        <v>63238.25</v>
+        <f>SUM(K25:M28)/4</f>
+        <v>282265.57500000001</v>
       </c>
       <c r="H91" t="str">
-        <f t="shared" si="2"/>
-        <v>113092,80781.35,82349.65,63238.25</v>
+        <f t="shared" si="1"/>
+        <v>472581.25,354581.45,362762.25,282265.575</v>
       </c>
       <c r="L91">
-        <f t="shared" si="1"/>
-        <v>11678.362853158727</v>
+        <f t="shared" ref="L91:L94" si="2">$C$155*$L$100*B91</f>
+        <v>31737.668459760775</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <f t="shared" si="0"/>
-        <v>2875761</v>
-      </c>
-      <c r="B92">
-        <v>3600</v>
+        <v>2396467.5</v>
+      </c>
+      <c r="B92" s="1">
+        <v>3000</v>
       </c>
       <c r="C92" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D92">
-        <f>SUM(B65:D68)/4</f>
-        <v>898944.25</v>
+        <f>SUM(B35:D38)/4</f>
+        <v>607253.75</v>
       </c>
       <c r="E92">
-        <f>SUM(E65:G68)/4</f>
-        <v>688793.5</v>
+        <f>SUM(E35:G38)/4</f>
+        <v>453880.02499999997</v>
       </c>
       <c r="F92">
-        <f>SUM(H65:J68)/4</f>
-        <v>719432.75</v>
+        <f>SUM(H35:J38)/4</f>
+        <v>468407</v>
       </c>
       <c r="G92">
-        <f>SUM(K65:M68)/4</f>
-        <v>549341.25</v>
+        <f>SUM(K35:M38)/4</f>
+        <v>360940.55</v>
       </c>
       <c r="H92" t="str">
+        <f t="shared" si="1"/>
+        <v>607253.75,453880.025,468407,360940.55</v>
+      </c>
+      <c r="L92">
         <f t="shared" si="2"/>
-        <v>898944.25,688793.5,719432.75,549341.25</v>
-      </c>
-      <c r="L92">
-        <f t="shared" ref="L92" si="3">$C$152*$L$97*B92</f>
-        <v>49461.301495731081</v>
+        <v>41217.751246442567</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <f t="shared" si="0"/>
+        <v>1318057.125</v>
+      </c>
+      <c r="B93" s="1">
+        <v>1650</v>
+      </c>
+      <c r="C93" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93">
+        <f>SUM(B45:D48)/4</f>
+        <v>641216</v>
+      </c>
+      <c r="E93">
+        <f>SUM(E45:G48)/4</f>
+        <v>507398.45</v>
+      </c>
+      <c r="F93">
+        <f>SUM(H45:J48)/4</f>
+        <v>565767</v>
+      </c>
+      <c r="G93">
+        <f>SUM(K45:M48)/4</f>
+        <v>403365.80000000005</v>
+      </c>
+      <c r="H93" t="str">
+        <f t="shared" si="1"/>
+        <v>641216,507398.45,565767,403365.8</v>
+      </c>
+      <c r="L93">
+        <f t="shared" si="2"/>
+        <v>22669.763185543412</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <f t="shared" si="0"/>
+        <v>678999.125</v>
+      </c>
+      <c r="B94" s="1">
+        <v>850</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D94">
+        <f>SUM(B55:D58)/4</f>
+        <v>113092</v>
+      </c>
+      <c r="E94">
+        <f>SUM(E55:G58)/4</f>
+        <v>80781.349999999991</v>
+      </c>
+      <c r="F94">
+        <f>SUM(H55:J58)/4</f>
+        <v>82349.649999999994</v>
+      </c>
+      <c r="G94">
+        <f>SUM(K55:M58)/4</f>
+        <v>63238.25</v>
+      </c>
+      <c r="H94" t="str">
+        <f t="shared" si="1"/>
+        <v>113092,80781.35,82349.65,63238.25</v>
+      </c>
+      <c r="L94">
+        <f t="shared" si="2"/>
+        <v>11678.362853158727</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <f t="shared" si="0"/>
+        <v>2875761</v>
+      </c>
+      <c r="B95">
+        <v>3600</v>
+      </c>
+      <c r="C95" t="s">
+        <v>85</v>
+      </c>
+      <c r="D95">
+        <f>SUM(B65:D68)/4</f>
+        <v>898944.25</v>
+      </c>
+      <c r="E95">
+        <f>SUM(E65:G68)/4</f>
+        <v>688793.5</v>
+      </c>
+      <c r="F95">
+        <f>SUM(H65:J68)/4</f>
+        <v>719432.75</v>
+      </c>
+      <c r="G95">
+        <f>SUM(K65:M68)/4</f>
+        <v>549341.25</v>
+      </c>
+      <c r="H95" t="str">
+        <f t="shared" si="1"/>
+        <v>898944.25,688793.5,719432.75,549341.25</v>
+      </c>
+      <c r="L95">
+        <f t="shared" ref="L95" si="3">$C$155*$L$100*B95</f>
+        <v>49461.301495731081</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <f t="shared" si="0"/>
         <v>3594701.25</v>
       </c>
-      <c r="B93">
+      <c r="B96">
         <v>4500</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C96" t="s">
         <v>86</v>
       </c>
-      <c r="D93">
+      <c r="D96">
         <f>SUM(B75:D78)/4</f>
         <v>1633809.25</v>
       </c>
-      <c r="E93">
+      <c r="E96">
         <f>SUM(E75:G78)/4</f>
         <v>1277711.5</v>
       </c>
-      <c r="F93">
+      <c r="F96">
         <f>SUM(H75:J78)/4</f>
         <v>1373549</v>
       </c>
-      <c r="G93">
+      <c r="G96">
         <f>SUM(K75:M78)/4</f>
         <v>1016046.5</v>
       </c>
-      <c r="H93" t="str">
-        <f t="shared" si="2"/>
+      <c r="H96" t="str">
+        <f t="shared" si="1"/>
         <v>1633809.25,1277711.5,1373549,1016046.5</v>
       </c>
-      <c r="L93">
-        <f>$C$152*$L$97*B93</f>
+      <c r="L96">
+        <f>$C$155*$L$100*B96</f>
         <v>61826.626869663851</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="L96" t="s">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L99" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B97" t="s">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B100" t="s">
         <v>25</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C100" t="s">
         <v>24</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D100" t="s">
         <v>49</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E100" t="s">
         <v>50</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F100" t="s">
         <v>51</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G100" t="s">
         <v>52</v>
       </c>
-      <c r="L97">
+      <c r="L100">
         <v>1.0756600000000001</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B98" s="1">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B101" s="1">
         <v>910</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C101" t="s">
         <v>23</v>
       </c>
-      <c r="D98">
-        <f>D86/$B98</f>
+      <c r="D101">
+        <f>D89/$B101</f>
         <v>149.1831043956044</v>
       </c>
-      <c r="E98">
-        <f t="shared" ref="E98:F98" si="4">E86/$B98</f>
+      <c r="E101">
+        <f t="shared" ref="E101:F101" si="4">E89/$B101</f>
         <v>111.22744505494506</v>
       </c>
-      <c r="F98">
+      <c r="F101">
         <f t="shared" si="4"/>
         <v>112.05090659340658</v>
       </c>
-      <c r="G98">
-        <f>G86/$B98</f>
+      <c r="G101">
+        <f>G89/$B101</f>
         <v>90.068269230769232</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B99" s="1">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B102" s="1">
         <v>2050</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C102" t="s">
         <v>39</v>
       </c>
-      <c r="D99">
-        <f t="shared" ref="D99:G99" si="5">D87/$B99</f>
+      <c r="D102">
+        <f t="shared" ref="D102:G102" si="5">D90/$B102</f>
         <v>294.62890243902439</v>
       </c>
-      <c r="E99">
+      <c r="E102">
         <f t="shared" si="5"/>
         <v>225.33557317073172</v>
       </c>
-      <c r="F99">
+      <c r="F102">
         <f t="shared" si="5"/>
         <v>235.9430487804878</v>
       </c>
-      <c r="G99">
+      <c r="G102">
         <f t="shared" si="5"/>
         <v>177.99464634146341</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B100" s="1">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B103" s="1">
         <v>2310</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="D100">
-        <f t="shared" ref="D100:G100" si="6">D88/$B100</f>
+      <c r="D103">
+        <f t="shared" ref="D103:G103" si="6">D91/$B103</f>
         <v>204.58062770562771</v>
       </c>
-      <c r="E100">
+      <c r="E103">
         <f t="shared" si="6"/>
         <v>153.49846320346319</v>
       </c>
-      <c r="F100">
+      <c r="F103">
         <f t="shared" si="6"/>
         <v>157.03993506493507</v>
       </c>
-      <c r="G100">
+      <c r="G103">
         <f t="shared" si="6"/>
         <v>122.19288961038961</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B101" s="1">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B104" s="1">
         <v>3000</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C104" t="s">
         <v>43</v>
       </c>
-      <c r="D101">
-        <f t="shared" ref="D101:G101" si="7">D89/$B101</f>
+      <c r="D104">
+        <f t="shared" ref="D104:G104" si="7">D92/$B104</f>
         <v>202.41791666666666</v>
       </c>
-      <c r="E101">
+      <c r="E104">
         <f t="shared" si="7"/>
         <v>151.29334166666666</v>
       </c>
-      <c r="F101">
+      <c r="F104">
         <f t="shared" si="7"/>
         <v>156.13566666666668</v>
       </c>
-      <c r="G101">
+      <c r="G104">
         <f t="shared" si="7"/>
         <v>120.31351666666666</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B102" s="1">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B105" s="1">
         <v>1650</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C105" t="s">
         <v>45</v>
       </c>
-      <c r="D102">
-        <f t="shared" ref="D102:G102" si="8">D90/$B102</f>
+      <c r="D105">
+        <f t="shared" ref="D105:G105" si="8">D93/$B105</f>
         <v>388.61575757575758</v>
       </c>
-      <c r="E102">
+      <c r="E105">
         <f t="shared" si="8"/>
         <v>307.51421212121215</v>
       </c>
-      <c r="F102">
+      <c r="F105">
         <f t="shared" si="8"/>
         <v>342.8890909090909</v>
       </c>
-      <c r="G102">
+      <c r="G105">
         <f t="shared" si="8"/>
         <v>244.46412121212123</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B103" s="1">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B106" s="1">
         <v>850</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D103">
-        <f t="shared" ref="D103:F103" si="9">D91/$B103</f>
+      <c r="D106">
+        <f t="shared" ref="D106:F106" si="9">D94/$B106</f>
         <v>133.04941176470589</v>
       </c>
-      <c r="E103">
+      <c r="E106">
         <f t="shared" si="9"/>
         <v>95.036882352941163</v>
       </c>
-      <c r="F103">
+      <c r="F106">
         <f t="shared" si="9"/>
         <v>96.881941176470576</v>
       </c>
-      <c r="G103">
-        <f>G91/$B103</f>
+      <c r="G106">
+        <f>G94/$B106</f>
         <v>74.397941176470582</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B112" s="14" t="s">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B115" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C112" s="14"/>
-      <c r="D112" s="14"/>
-      <c r="E112" s="14"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F113" t="s">
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F116" t="s">
         <v>72</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G116" t="s">
         <v>73</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H116" t="s">
         <v>74</v>
       </c>
-      <c r="I113" s="12" t="s">
+      <c r="I116" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="J113" s="12"/>
-      <c r="K113" s="12"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>92</v>
-      </c>
-      <c r="B114" t="s">
-        <v>60</v>
-      </c>
-      <c r="C114">
-        <v>21722000</v>
-      </c>
-      <c r="F114">
-        <v>16000000</v>
-      </c>
-      <c r="G114">
-        <v>3171740</v>
-      </c>
-      <c r="H114">
-        <v>1650000</v>
-      </c>
-      <c r="I114" s="13">
-        <v>900000</v>
-      </c>
-      <c r="J114" s="13"/>
-      <c r="K114" s="13"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>92</v>
-      </c>
-      <c r="B115" t="s">
-        <v>61</v>
-      </c>
-      <c r="C115">
-        <f>C114/24</f>
-        <v>905083.33333333337</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>93</v>
-      </c>
-      <c r="B116" t="s">
-        <v>60</v>
-      </c>
-      <c r="C116">
-        <f>F114+G114</f>
-        <v>19171740</v>
-      </c>
+      <c r="J116" s="12"/>
+      <c r="K116" s="12"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
+        <v>92</v>
+      </c>
+      <c r="B117" t="s">
+        <v>60</v>
+      </c>
+      <c r="C117">
+        <v>21722000</v>
+      </c>
+      <c r="F117">
+        <v>16000000</v>
+      </c>
+      <c r="G117">
+        <v>3171740</v>
+      </c>
+      <c r="H117">
+        <v>1650000</v>
+      </c>
+      <c r="I117" s="13">
+        <v>900000</v>
+      </c>
+      <c r="J117" s="13"/>
+      <c r="K117" s="13"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>92</v>
+      </c>
+      <c r="B118" t="s">
+        <v>61</v>
+      </c>
+      <c r="C118">
+        <f>C117/24</f>
+        <v>905083.33333333337</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
         <v>93</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B119" t="s">
+        <v>60</v>
+      </c>
+      <c r="C119">
+        <f>F117+G117</f>
+        <v>19171740</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>93</v>
+      </c>
+      <c r="B120" t="s">
         <v>61</v>
       </c>
-      <c r="C117">
-        <f>C116/24</f>
+      <c r="C120">
+        <f>C119/24</f>
         <v>798822.5</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G118">
-        <f>1-(G114/(G114+F114))</f>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G121">
+        <f>1-(G117/(G117+F117))</f>
         <v>0.83456170384117456</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G119">
-        <f>1-2*(G114/(F114+G114))</f>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G122">
+        <f>1-2*(G117/(F117+G117))</f>
         <v>0.66912340768234913</v>
       </c>
-      <c r="H119">
+      <c r="H122">
         <f>0.67</f>
         <v>0.67</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B120" s="15" t="s">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B123" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C120" s="15"/>
-      <c r="G120">
-        <f>G119/25</f>
+      <c r="C123" s="15"/>
+      <c r="G123">
+        <f>G122/25</f>
         <v>2.6764936307293964E-2</v>
       </c>
-      <c r="H120">
-        <f>H119/25</f>
+      <c r="H123">
+        <f>H122/25</f>
         <v>2.6800000000000001E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B122" t="s">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B125" t="s">
         <v>61</v>
       </c>
-      <c r="C122">
+      <c r="C125">
         <v>922550</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F122">
-        <f>SUM(F114:K114)</f>
+      <c r="F125">
+        <f>SUM(F117:K117)</f>
         <v>21721740</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B123" t="s">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B126" t="s">
         <v>61</v>
       </c>
-      <c r="C123">
-        <f>C122*L97</f>
+      <c r="C126">
+        <f>C125*L100</f>
         <v>992350.13300000003</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F123">
-        <f>(F114+G114)/F122</f>
+      <c r="F126">
+        <f>(F117+G117)/F125</f>
         <v>0.88260608956741038</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B125" s="14" t="s">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B128" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C125" s="14"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B127" t="s">
+      <c r="C128" s="14"/>
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B130" t="s">
         <v>61</v>
       </c>
-      <c r="C127">
+      <c r="C130">
         <v>310804.5</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B128" t="s">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
         <v>61</v>
       </c>
-      <c r="C128">
-        <f>C127*L97</f>
+      <c r="C131">
+        <f>C130*L100</f>
         <v>334319.96847000002</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H133" s="4"/>
-    </row>
-    <row r="134" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B134" s="12" t="s">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H136" s="4"/>
+    </row>
+    <row r="137" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B137" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C134" s="12"/>
-      <c r="D134" s="12"/>
-      <c r="H134" s="5"/>
-      <c r="I134" s="5"/>
-    </row>
-    <row r="135" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="8"/>
-      <c r="C135" s="11" t="s">
+      <c r="C137" s="12"/>
+      <c r="D137" s="12"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5"/>
+    </row>
+    <row r="138" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B138" s="8"/>
+      <c r="C138" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D135" s="9" t="s">
+      <c r="D138" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="H135" s="6"/>
-      <c r="I135" s="7"/>
-    </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B136" s="10">
-        <v>2008</v>
-      </c>
-      <c r="C136" s="7">
-        <v>71.740857299243771</v>
-      </c>
-      <c r="D136" s="9"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="7"/>
-    </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B137" s="10">
-        <v>2009</v>
-      </c>
-      <c r="C137" s="7">
-        <v>69.888415432558389</v>
-      </c>
-      <c r="D137" s="9">
-        <f>LN(C137/C136)</f>
-        <v>-2.6160517193397299E-2</v>
-      </c>
-      <c r="H137" s="6"/>
-      <c r="I137" s="7"/>
-    </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B138" s="10">
-        <v>2010</v>
-      </c>
-      <c r="C138" s="7">
-        <v>62.93535169148111</v>
-      </c>
-      <c r="D138" s="9">
-        <f t="shared" ref="D138:D150" si="10">LN(C138/C137)</f>
-        <v>-0.10479186902848212</v>
       </c>
       <c r="H138" s="6"/>
       <c r="I138" s="7"/>
     </row>
     <row r="139" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B139" s="10">
+        <v>2008</v>
+      </c>
+      <c r="C139" s="7">
+        <v>71.740857299243771</v>
+      </c>
+      <c r="D139" s="9"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B140" s="10">
+        <v>2009</v>
+      </c>
+      <c r="C140" s="7">
+        <v>69.888415432558389</v>
+      </c>
+      <c r="D140" s="9">
+        <f>LN(C140/C139)</f>
+        <v>-2.6160517193397299E-2</v>
+      </c>
+      <c r="H140" s="6"/>
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B141" s="10">
+        <v>2010</v>
+      </c>
+      <c r="C141" s="7">
+        <v>62.93535169148111</v>
+      </c>
+      <c r="D141" s="9">
+        <f t="shared" ref="D141:D153" si="10">LN(C141/C140)</f>
+        <v>-0.10479186902848212</v>
+      </c>
+      <c r="H141" s="6"/>
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B142" s="10">
         <v>2011</v>
       </c>
-      <c r="C139" s="7">
+      <c r="C142" s="7">
         <v>66.433836808366976</v>
       </c>
-      <c r="D139" s="9">
+      <c r="D142" s="9">
         <f t="shared" si="10"/>
         <v>5.4098481274815029E-2</v>
       </c>
-      <c r="H139" s="6"/>
-      <c r="I139" s="7"/>
-    </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B140" s="10">
+      <c r="H142" s="6"/>
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B143" s="10">
         <v>2012</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C143" s="7">
         <v>45.124106043118374</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D143" s="9">
         <f t="shared" si="10"/>
         <v>-0.38678991139471014</v>
       </c>
-      <c r="H140" s="6"/>
-      <c r="I140" s="7"/>
-    </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B141" s="10">
+      <c r="H143" s="6"/>
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B144" s="10">
         <v>2013</v>
       </c>
-      <c r="C141" s="7">
+      <c r="C144" s="7">
         <v>63.346117847874872</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D144" s="9">
         <f t="shared" si="10"/>
         <v>0.33919701809916086</v>
       </c>
-      <c r="H141" s="6"/>
-      <c r="I141" s="7"/>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B142" s="10">
+      <c r="H144" s="6"/>
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B145" s="10">
         <v>2014</v>
       </c>
-      <c r="C142" s="7">
+      <c r="C145" s="7">
         <v>35.287203699362649</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D145" s="9">
         <f t="shared" si="10"/>
         <v>-0.58509322709191702</v>
       </c>
-      <c r="H142" s="6"/>
-      <c r="I142" s="7"/>
-    </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B143" s="10">
+      <c r="H145" s="6"/>
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B146" s="10">
         <v>2015</v>
       </c>
-      <c r="C143" s="7">
+      <c r="C146" s="7">
         <v>25.69618952009867</v>
       </c>
-      <c r="D143" s="9">
+      <c r="D146" s="9">
         <f t="shared" si="10"/>
         <v>-0.31717768357724624</v>
       </c>
-      <c r="H143" s="6"/>
-      <c r="I143" s="7"/>
-    </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B144" s="10">
+      <c r="H146" s="6"/>
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B147" s="10">
         <v>2016</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C147" s="7">
         <v>31.300854676277297</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D147" s="9">
         <f t="shared" si="10"/>
         <v>0.19730268991666705</v>
       </c>
-      <c r="H144" s="6"/>
-      <c r="I144" s="7"/>
-    </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B145" s="10">
+      <c r="H147" s="6"/>
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B148" s="10">
         <v>2017</v>
       </c>
-      <c r="C145" s="7">
+      <c r="C148" s="7">
         <v>24.553162386815192</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D148" s="9">
         <f t="shared" si="10"/>
         <v>-0.24280474305306415</v>
       </c>
-      <c r="H145" s="6"/>
-      <c r="I145" s="7"/>
-    </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B146" s="10">
+      <c r="H148" s="6"/>
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B149" s="10">
         <v>2018</v>
       </c>
-      <c r="C146" s="7">
+      <c r="C149" s="7">
         <v>21.272921972468328</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D149" s="9">
         <f t="shared" si="10"/>
         <v>-0.14340566500221763</v>
       </c>
-      <c r="H146" s="6"/>
-      <c r="I146" s="7"/>
-    </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B147" s="10">
+      <c r="H149" s="6"/>
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B150" s="10">
         <v>2019</v>
       </c>
-      <c r="C147" s="7">
+      <c r="C150" s="7">
         <v>18.366067363877619</v>
       </c>
-      <c r="D147" s="9">
+      <c r="D150" s="9">
         <f t="shared" si="10"/>
         <v>-0.14693019802690385</v>
       </c>
-      <c r="H147" s="6"/>
-      <c r="I147" s="7"/>
-    </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B148" s="10">
+      <c r="H150" s="6"/>
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B151" s="10">
         <v>2020</v>
       </c>
-      <c r="C148" s="7">
+      <c r="C151" s="7">
         <v>20.000293309725464</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D151" s="9">
         <f t="shared" si="10"/>
         <v>8.5242141890254391E-2</v>
       </c>
-      <c r="H148" s="6"/>
-      <c r="I148" s="7"/>
-    </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B149" s="10">
+      <c r="H151" s="6"/>
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B152" s="10">
         <v>2021</v>
       </c>
-      <c r="C149" s="7">
+      <c r="C152" s="7">
         <v>16.160397699393901</v>
       </c>
-      <c r="D149" s="9">
+      <c r="D152" s="9">
         <f t="shared" si="10"/>
         <v>-0.21318327603159284</v>
       </c>
-      <c r="H149" s="6"/>
-      <c r="I149" s="7"/>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B150" s="10">
+      <c r="H152" s="6"/>
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B153" s="10">
         <v>2022</v>
       </c>
-      <c r="C150" s="7">
+      <c r="C153" s="7">
         <v>15.847940714652479</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D153" s="9">
         <f t="shared" si="10"/>
         <v>-1.9524094384390369E-2</v>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C151">
-        <f>C150*$F$154</f>
-        <v>14.227560105927731</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C152">
-        <f t="shared" ref="C152:C158" si="11">C151*$F$154</f>
-        <v>12.772856121340251</v>
-      </c>
-    </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C153">
-        <f t="shared" si="11"/>
-        <v>11.466889071759146</v>
-      </c>
-      <c r="F153">
-        <f>AVERAGE(D137:D150)</f>
-        <v>-0.10785863240021601</v>
-      </c>
-    </row>
     <row r="154" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C154">
-        <f t="shared" si="11"/>
-        <v>10.294451275024008</v>
-      </c>
-      <c r="F154">
-        <f>EXP(F153)</f>
-        <v>0.89775450085911801</v>
+        <f>C153*$F$157</f>
+        <v>14.227560105927731</v>
       </c>
     </row>
     <row r="155" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C155">
-        <f t="shared" si="11"/>
-        <v>9.2418899660276885</v>
+        <f t="shared" ref="C155:C161" si="11">C154*$F$157</f>
+        <v>12.772856121340251</v>
       </c>
     </row>
     <row r="156" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C156">
         <f t="shared" si="11"/>
-        <v>8.2969483134460784</v>
+        <v>11.466889071759146</v>
+      </c>
+      <c r="F156">
+        <f>AVERAGE(D140:D153)</f>
+        <v>-0.10785863240021601</v>
       </c>
     </row>
     <row r="157" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C157">
         <f t="shared" si="11"/>
-        <v>7.4486226917916856</v>
+        <v>10.294451275024008</v>
+      </c>
+      <c r="F157">
+        <f>EXP(F156)</f>
+        <v>0.89775450085911801</v>
       </c>
     </row>
     <row r="158" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C158">
         <f t="shared" si="11"/>
+        <v>9.2418899660276885</v>
+      </c>
+    </row>
+    <row r="159" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C159">
+        <f t="shared" si="11"/>
+        <v>8.2969483134460784</v>
+      </c>
+    </row>
+    <row r="160" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C160">
+        <f t="shared" si="11"/>
+        <v>7.4486226917916856</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C161">
+        <f t="shared" si="11"/>
         <v>6.6870345467573449</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="I113:K113"/>
-    <mergeCell ref="I114:K114"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="D84:G84"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="I116:K116"/>
+    <mergeCell ref="I117:K117"/>
+    <mergeCell ref="B137:D137"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B128:C128"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65B165-A228-534D-890C-7BD6A0C7E246}">
   <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/Data/Wind Power.xlsx
+++ b/Data/Wind Power.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EC68F3-7E3D-9A44-824E-9CB53FB6B9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316FBF3B-B1B6-0C4D-A9B1-E45CCF2FEB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="109">
   <si>
     <t>Metrics</t>
   </si>
@@ -362,6 +362,12 @@
   </si>
   <si>
     <t>Spatial Requirement m^2</t>
+  </si>
+  <si>
+    <t>O&amp;M costs (2024  USD/kW/year) IRENA</t>
+  </si>
+  <si>
+    <t>Average Turbine Price 2024$/kW</t>
   </si>
 </sst>
 </file>
@@ -11096,15 +11102,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>362238</xdr:colOff>
-      <xdr:row>135</xdr:row>
-      <xdr:rowOff>129308</xdr:rowOff>
+      <xdr:colOff>514638</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>112375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>43295</xdr:colOff>
-      <xdr:row>152</xdr:row>
-      <xdr:rowOff>43295</xdr:rowOff>
+      <xdr:colOff>195695</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>26362</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11132,15 +11138,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>847132</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>107741</xdr:rowOff>
+      <xdr:colOff>728599</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>73874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>674077</xdr:colOff>
-      <xdr:row>167</xdr:row>
-      <xdr:rowOff>129513</xdr:rowOff>
+      <xdr:colOff>555544</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>95646</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11172,16 +11178,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>687916</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>529167</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11208,16 +11214,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>738716</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>656167</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12599,7 +12605,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6B8A3E-987F-534C-BE5F-E1607AAFBDBF}">
-  <dimension ref="A1:Y161"/>
+  <dimension ref="A1:Y171"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
@@ -12610,6 +12616,7 @@
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="30.1640625" customWidth="1"/>
     <col min="8" max="8" width="21.1640625" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
@@ -15210,7 +15217,7 @@
       </c>
       <c r="C128" s="14"/>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
         <v>61</v>
       </c>
@@ -15221,7 +15228,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
         <v>61</v>
       </c>
@@ -15233,19 +15240,36 @@
         <v>65</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="M135" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="136" spans="2:16" x14ac:dyDescent="0.2">
       <c r="H136" s="4"/>
-    </row>
-    <row r="137" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M136">
+        <v>1.0756600000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B137" s="12" t="s">
         <v>81</v>
       </c>
       <c r="C137" s="12"/>
       <c r="D137" s="12"/>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
-    </row>
-    <row r="138" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M137" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="N137" s="12"/>
+      <c r="O137" s="12"/>
+      <c r="P137" s="12"/>
+    </row>
+    <row r="138" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B138" s="8"/>
       <c r="C138" s="11" t="s">
         <v>82</v>
@@ -15255,8 +15279,11 @@
       </c>
       <c r="H138" s="6"/>
       <c r="I138" s="7"/>
-    </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="N138" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="139" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B139" s="10">
         <v>2008</v>
       </c>
@@ -15266,8 +15293,15 @@
       <c r="D139" s="9"/>
       <c r="H139" s="6"/>
       <c r="I139" s="7"/>
-    </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M139" s="10">
+        <v>2008</v>
+      </c>
+      <c r="N139">
+        <f>C139*$M$136</f>
+        <v>77.168770562504562</v>
+      </c>
+    </row>
+    <row r="140" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B140" s="10">
         <v>2009</v>
       </c>
@@ -15280,8 +15314,15 @@
       </c>
       <c r="H140" s="6"/>
       <c r="I140" s="7"/>
-    </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M140" s="10">
+        <v>2009</v>
+      </c>
+      <c r="N140">
+        <f t="shared" ref="N140:N171" si="10">C140*$M$136</f>
+        <v>75.176172944185765</v>
+      </c>
+    </row>
+    <row r="141" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B141" s="10">
         <v>2010</v>
       </c>
@@ -15289,13 +15330,20 @@
         <v>62.93535169148111</v>
       </c>
       <c r="D141" s="9">
-        <f t="shared" ref="D141:D153" si="10">LN(C141/C140)</f>
+        <f t="shared" ref="D141:D153" si="11">LN(C141/C140)</f>
         <v>-0.10479186902848212</v>
       </c>
       <c r="H141" s="6"/>
       <c r="I141" s="7"/>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M141" s="10">
+        <v>2010</v>
+      </c>
+      <c r="N141">
+        <f t="shared" si="10"/>
+        <v>67.697040400458576</v>
+      </c>
+    </row>
+    <row r="142" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B142" s="10">
         <v>2011</v>
       </c>
@@ -15303,13 +15351,20 @@
         <v>66.433836808366976</v>
       </c>
       <c r="D142" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.4098481274815029E-2</v>
       </c>
       <c r="H142" s="6"/>
       <c r="I142" s="7"/>
-    </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M142" s="10">
+        <v>2011</v>
+      </c>
+      <c r="N142">
+        <f t="shared" si="10"/>
+        <v>71.460220901288025</v>
+      </c>
+    </row>
+    <row r="143" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B143" s="10">
         <v>2012</v>
       </c>
@@ -15317,13 +15372,20 @@
         <v>45.124106043118374</v>
       </c>
       <c r="D143" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.38678991139471014</v>
       </c>
       <c r="H143" s="6"/>
       <c r="I143" s="7"/>
-    </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M143" s="10">
+        <v>2012</v>
+      </c>
+      <c r="N143">
+        <f t="shared" si="10"/>
+        <v>48.538195906340711</v>
+      </c>
+    </row>
+    <row r="144" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B144" s="10">
         <v>2013</v>
       </c>
@@ -15331,13 +15393,20 @@
         <v>63.346117847874872</v>
       </c>
       <c r="D144" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33919701809916086</v>
       </c>
       <c r="H144" s="6"/>
       <c r="I144" s="7"/>
-    </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M144" s="10">
+        <v>2013</v>
+      </c>
+      <c r="N144">
+        <f t="shared" si="10"/>
+        <v>68.138885124245093</v>
+      </c>
+    </row>
+    <row r="145" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B145" s="10">
         <v>2014</v>
       </c>
@@ -15345,13 +15414,20 @@
         <v>35.287203699362649</v>
       </c>
       <c r="D145" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.58509322709191702</v>
       </c>
       <c r="H145" s="6"/>
       <c r="I145" s="7"/>
-    </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M145" s="10">
+        <v>2014</v>
+      </c>
+      <c r="N145">
+        <f t="shared" si="10"/>
+        <v>37.957033531256428</v>
+      </c>
+    </row>
+    <row r="146" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B146" s="10">
         <v>2015</v>
       </c>
@@ -15359,13 +15435,20 @@
         <v>25.69618952009867</v>
       </c>
       <c r="D146" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.31717768357724624</v>
       </c>
       <c r="H146" s="6"/>
       <c r="I146" s="7"/>
-    </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M146" s="10">
+        <v>2015</v>
+      </c>
+      <c r="N146">
+        <f t="shared" si="10"/>
+        <v>27.640363219189336</v>
+      </c>
+    </row>
+    <row r="147" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B147" s="10">
         <v>2016</v>
       </c>
@@ -15373,13 +15456,20 @@
         <v>31.300854676277297</v>
       </c>
       <c r="D147" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.19730268991666705</v>
       </c>
       <c r="H147" s="6"/>
       <c r="I147" s="7"/>
-    </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M147" s="10">
+        <v>2016</v>
+      </c>
+      <c r="N147">
+        <f t="shared" si="10"/>
+        <v>33.669077341084439</v>
+      </c>
+    </row>
+    <row r="148" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B148" s="10">
         <v>2017</v>
       </c>
@@ -15387,13 +15477,20 @@
         <v>24.553162386815192</v>
       </c>
       <c r="D148" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.24280474305306415</v>
       </c>
       <c r="H148" s="6"/>
       <c r="I148" s="7"/>
-    </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M148" s="10">
+        <v>2017</v>
+      </c>
+      <c r="N148">
+        <f t="shared" si="10"/>
+        <v>26.410854653001632</v>
+      </c>
+    </row>
+    <row r="149" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B149" s="10">
         <v>2018</v>
       </c>
@@ -15401,13 +15498,20 @@
         <v>21.272921972468328</v>
       </c>
       <c r="D149" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.14340566500221763</v>
       </c>
       <c r="H149" s="6"/>
       <c r="I149" s="7"/>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M149" s="10">
+        <v>2018</v>
+      </c>
+      <c r="N149">
+        <f t="shared" si="10"/>
+        <v>22.882431248905284</v>
+      </c>
+    </row>
+    <row r="150" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B150" s="10">
         <v>2019</v>
       </c>
@@ -15415,13 +15519,20 @@
         <v>18.366067363877619</v>
       </c>
       <c r="D150" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.14693019802690385</v>
       </c>
       <c r="H150" s="6"/>
       <c r="I150" s="7"/>
-    </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M150" s="10">
+        <v>2019</v>
+      </c>
+      <c r="N150">
+        <f t="shared" si="10"/>
+        <v>19.755644020628601</v>
+      </c>
+    </row>
+    <row r="151" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B151" s="10">
         <v>2020</v>
       </c>
@@ -15429,13 +15540,20 @@
         <v>20.000293309725464</v>
       </c>
       <c r="D151" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.5242141890254391E-2</v>
       </c>
       <c r="H151" s="6"/>
       <c r="I151" s="7"/>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M151" s="10">
+        <v>2020</v>
+      </c>
+      <c r="N151">
+        <f t="shared" si="10"/>
+        <v>21.513515501539295</v>
+      </c>
+    </row>
+    <row r="152" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B152" s="10">
         <v>2021</v>
       </c>
@@ -15443,13 +15561,20 @@
         <v>16.160397699393901</v>
       </c>
       <c r="D152" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.21318327603159284</v>
       </c>
       <c r="H152" s="6"/>
       <c r="I152" s="7"/>
-    </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M152" s="10">
+        <v>2021</v>
+      </c>
+      <c r="N152">
+        <f t="shared" si="10"/>
+        <v>17.383093389330043</v>
+      </c>
+    </row>
+    <row r="153" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B153" s="10">
         <v>2022</v>
       </c>
@@ -15457,75 +15582,291 @@
         <v>15.847940714652479</v>
       </c>
       <c r="D153" s="9">
+        <f t="shared" si="11"/>
+        <v>-1.9524094384390369E-2</v>
+      </c>
+      <c r="M153" s="10">
+        <v>2022</v>
+      </c>
+      <c r="N153">
         <f t="shared" si="10"/>
-        <v>-1.9524094384390369E-2</v>
-      </c>
-    </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.2">
+        <v>17.046995909123087</v>
+      </c>
+    </row>
+    <row r="154" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C154">
         <f>C153*$F$157</f>
         <v>14.227560105927731</v>
       </c>
-    </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M154" s="10">
+        <v>2023</v>
+      </c>
+      <c r="N154">
+        <f t="shared" si="10"/>
+        <v>15.304017303542224</v>
+      </c>
+      <c r="P154">
+        <v>15.304017303542224</v>
+      </c>
+    </row>
+    <row r="155" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C155">
-        <f t="shared" ref="C155:C161" si="11">C154*$F$157</f>
+        <f t="shared" ref="C155:C171" si="12">C154*$F$157</f>
         <v>12.772856121340251</v>
       </c>
-    </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M155" s="10">
+        <v>2024</v>
+      </c>
+      <c r="N155">
+        <f t="shared" si="10"/>
+        <v>13.739250415480855</v>
+      </c>
+      <c r="P155">
+        <v>13.739250415480855</v>
+      </c>
+    </row>
+    <row r="156" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11.466889071759146</v>
       </c>
       <c r="F156">
         <f>AVERAGE(D140:D153)</f>
         <v>-0.10785863240021601</v>
       </c>
-    </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M156" s="10">
+        <v>2025</v>
+      </c>
+      <c r="N156">
+        <f t="shared" si="10"/>
+        <v>12.334473898928444</v>
+      </c>
+      <c r="P156">
+        <v>12.334473898928444</v>
+      </c>
+    </row>
+    <row r="157" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C157">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.294451275024008</v>
       </c>
       <c r="F157">
         <f>EXP(F156)</f>
         <v>0.89775450085911801</v>
       </c>
-    </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M157" s="10">
+        <v>2026</v>
+      </c>
+      <c r="N157">
+        <f t="shared" si="10"/>
+        <v>11.073329458492324</v>
+      </c>
+    </row>
+    <row r="158" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C158">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.2418899660276885</v>
       </c>
-    </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M158" s="10">
+        <v>2027</v>
+      </c>
+      <c r="N158">
+        <f t="shared" si="10"/>
+        <v>9.9411313608573444</v>
+      </c>
+      <c r="P158">
+        <v>9.9411313608573444</v>
+      </c>
+    </row>
+    <row r="159" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C159">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.2969483134460784</v>
       </c>
-    </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="M159" s="10">
+        <v>2028</v>
+      </c>
+      <c r="N159">
+        <f t="shared" si="10"/>
+        <v>8.9246954228414097</v>
+      </c>
+    </row>
+    <row r="160" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C160">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.4486226917916856</v>
       </c>
-    </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="M160" s="10">
+        <v>2029</v>
+      </c>
+      <c r="N160">
+        <f t="shared" si="10"/>
+        <v>8.0121854846526457</v>
+      </c>
+    </row>
+    <row r="161" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C161">
-        <f t="shared" si="11"/>
+        <f>C160*$F$157</f>
         <v>6.6870345467573449</v>
       </c>
+      <c r="M161" s="10">
+        <v>2030</v>
+      </c>
+      <c r="N161">
+        <f t="shared" si="10"/>
+        <v>7.1929755805650064</v>
+      </c>
+      <c r="P161">
+        <v>7.1929755805650064</v>
+      </c>
+    </row>
+    <row r="162" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C162">
+        <f t="shared" si="12"/>
+        <v>6.0033153617518185</v>
+      </c>
+      <c r="M162" s="10">
+        <v>2031</v>
+      </c>
+      <c r="N162">
+        <f t="shared" si="10"/>
+        <v>6.4575262020219615</v>
+      </c>
+    </row>
+    <row r="163" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C163">
+        <f t="shared" si="12"/>
+        <v>5.3895033860893795</v>
+      </c>
+      <c r="M163" s="10">
+        <v>2032</v>
+      </c>
+      <c r="N163">
+        <f t="shared" si="10"/>
+        <v>5.7972732122809019</v>
+      </c>
+    </row>
+    <row r="164" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C164">
+        <f t="shared" si="12"/>
+        <v>4.8384509222571976</v>
+      </c>
+      <c r="M164" s="10">
+        <v>2033</v>
+      </c>
+      <c r="N164">
+        <f t="shared" si="10"/>
+        <v>5.2045281190351771</v>
+      </c>
+    </row>
+    <row r="165" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C165">
+        <f t="shared" si="12"/>
+        <v>4.3437410926423494</v>
+      </c>
+      <c r="M165" s="10">
+        <v>2034</v>
+      </c>
+      <c r="N165">
+        <f t="shared" si="10"/>
+        <v>4.6723885437116701</v>
+      </c>
+    </row>
+    <row r="166" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C166">
+        <f t="shared" si="12"/>
+        <v>3.8996131164863721</v>
+      </c>
+      <c r="M166" s="10">
+        <v>2035</v>
+      </c>
+      <c r="N166">
+        <f t="shared" si="10"/>
+        <v>4.1946578448797309</v>
+      </c>
+      <c r="P166">
+        <v>4.1946578448797309</v>
+      </c>
+    </row>
+    <row r="167" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C167">
+        <f t="shared" si="12"/>
+        <v>3.5008952269348925</v>
+      </c>
+      <c r="M167" s="10">
+        <v>2036</v>
+      </c>
+      <c r="N167">
+        <f t="shared" si="10"/>
+        <v>3.7657729598047869</v>
+      </c>
+    </row>
+    <row r="168" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C168">
+        <f t="shared" si="12"/>
+        <v>3.1429444470170029</v>
+      </c>
+      <c r="M168" s="10">
+        <v>2037</v>
+      </c>
+      <c r="N168">
+        <f t="shared" si="10"/>
+        <v>3.3807396238783096</v>
+      </c>
+    </row>
+    <row r="169" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C169">
+        <f t="shared" si="12"/>
+        <v>2.8215925232596861</v>
+      </c>
+      <c r="M169" s="10">
+        <v>2038</v>
+      </c>
+      <c r="N169">
+        <f t="shared" si="10"/>
+        <v>3.0350742135695143</v>
+      </c>
+    </row>
+    <row r="170" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C170">
+        <f t="shared" si="12"/>
+        <v>2.5330973873468188</v>
+      </c>
+      <c r="M170" s="10">
+        <v>2039</v>
+      </c>
+      <c r="N170">
+        <f t="shared" si="10"/>
+        <v>2.7247515356734793</v>
+      </c>
+    </row>
+    <row r="171" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="C171">
+        <f t="shared" si="12"/>
+        <v>2.2740995806050792</v>
+      </c>
+      <c r="M171" s="10">
+        <v>2040</v>
+      </c>
+      <c r="N171">
+        <f t="shared" si="10"/>
+        <v>2.4461579548736596</v>
+      </c>
+      <c r="P171">
+        <v>2.4461579548736596</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="I116:K116"/>
-    <mergeCell ref="I117:K117"/>
-    <mergeCell ref="B137:D137"/>
+  <mergeCells count="9">
     <mergeCell ref="D87:G87"/>
     <mergeCell ref="B115:E115"/>
     <mergeCell ref="B123:C123"/>
     <mergeCell ref="B128:C128"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="M137:P137"/>
+    <mergeCell ref="I116:K116"/>
+    <mergeCell ref="I117:K117"/>
+    <mergeCell ref="B137:D137"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15534,15 +15875,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65B165-A228-534D-890C-7BD6A0C7E246}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="28.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>96</v>
       </c>
@@ -15558,8 +15899,11 @@
       <c r="J1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2005</v>
       </c>
@@ -15572,8 +15916,12 @@
       <c r="J2">
         <v>2084.37</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2">
+        <f>J2*$E$7</f>
+        <v>2242.0734342000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2006</v>
       </c>
@@ -15590,8 +15938,12 @@
       <c r="J3">
         <v>2126.31</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3">
+        <f t="shared" ref="K3:K37" si="0">J3*$E$7</f>
+        <v>2287.1866146000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2007</v>
       </c>
@@ -15599,7 +15951,7 @@
         <v>2137.58</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C19" si="0">-LN(B4/B3)</f>
+        <f t="shared" ref="C4:C19" si="1">-LN(B4/B3)</f>
         <v>-5.2862650043141654E-3</v>
       </c>
       <c r="I4">
@@ -15608,8 +15960,12 @@
       <c r="J4">
         <v>2137.58</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>2299.3093027999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2008</v>
       </c>
@@ -15617,7 +15973,7 @@
         <v>2260.12</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-5.5743561190718972E-2</v>
       </c>
       <c r="I5">
@@ -15626,8 +15982,12 @@
       <c r="J5">
         <v>2260.12</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>2431.1206791999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2009</v>
       </c>
@@ -15635,8 +15995,11 @@
         <v>2299.9899999999998</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1.748686587985197E-2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>79</v>
       </c>
       <c r="I6">
         <v>2009</v>
@@ -15644,8 +16007,12 @@
       <c r="J6">
         <v>2299.9899999999998</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>2474.0072433999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2010</v>
       </c>
@@ -15653,8 +16020,11 @@
         <v>2173.08</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.6759259040450892E-2</v>
+      </c>
+      <c r="E7">
+        <v>1.0756600000000001</v>
       </c>
       <c r="I7">
         <v>2010</v>
@@ -15662,8 +16032,12 @@
       <c r="J7">
         <v>2173.08</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>2337.4952327999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2011</v>
       </c>
@@ -15671,7 +16045,7 @@
         <v>2148.79</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.124062304334523E-2</v>
       </c>
       <c r="I8">
@@ -15680,8 +16054,12 @@
       <c r="J8">
         <v>2148.79</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>2311.3674513999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2012</v>
       </c>
@@ -15689,7 +16067,7 @@
         <v>2212.5500000000002</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-2.9240803498884586E-2</v>
       </c>
       <c r="I9">
@@ -15698,8 +16076,12 @@
       <c r="J9">
         <v>2212.5500000000002</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>2379.9515330000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2013</v>
       </c>
@@ -15707,7 +16089,7 @@
         <v>2042.08</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.0176800262409961E-2</v>
       </c>
       <c r="I10">
@@ -15716,8 +16098,12 @@
       <c r="J10">
         <v>2042.08</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>2196.5837728000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2014</v>
       </c>
@@ -15725,7 +16111,7 @@
         <v>1995.33</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.3159446055892263E-2</v>
       </c>
       <c r="I11">
@@ -15734,8 +16120,12 @@
       <c r="J11">
         <v>1995.33</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>2146.2966678000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2015</v>
       </c>
@@ -15743,7 +16133,7 @@
         <v>1839.57</v>
       </c>
       <c r="C12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.1277601538714855E-2</v>
       </c>
       <c r="I12">
@@ -15752,8 +16142,12 @@
       <c r="J12">
         <v>1839.57</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>1978.7518662</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2016</v>
       </c>
@@ -15761,7 +16155,7 @@
         <v>1828.81</v>
       </c>
       <c r="C13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.8663665476852995E-3</v>
       </c>
       <c r="I13">
@@ -15770,8 +16164,12 @@
       <c r="J13">
         <v>1828.81</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>1967.1777646</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2017</v>
       </c>
@@ -15779,7 +16177,7 @@
         <v>1825.41</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.8608627729744384E-3</v>
       </c>
       <c r="I14">
@@ -15788,8 +16186,12 @@
       <c r="J14">
         <v>1825.41</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>1963.5205206000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -15797,7 +16199,7 @@
         <v>1740.75</v>
       </c>
       <c r="C15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.748856449645749E-2</v>
       </c>
       <c r="I15">
@@ -15806,8 +16208,12 @@
       <c r="J15">
         <v>1740.75</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>1872.4551450000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2019</v>
       </c>
@@ -15815,7 +16221,7 @@
         <v>1653.1</v>
       </c>
       <c r="C16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.1663741763689756E-2</v>
       </c>
       <c r="I16">
@@ -15824,8 +16230,12 @@
       <c r="J16">
         <v>1653.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>1778.173546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -15833,7 +16243,7 @@
         <v>1496.35</v>
       </c>
       <c r="C17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.9623503669014887E-2</v>
       </c>
       <c r="I17">
@@ -15842,8 +16252,12 @@
       <c r="J17">
         <v>1496.35</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>1609.5638409999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2021</v>
       </c>
@@ -15851,7 +16265,7 @@
         <v>1418.18</v>
       </c>
       <c r="C18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.3654450002797408E-2</v>
       </c>
       <c r="I18">
@@ -15860,8 +16274,12 @@
       <c r="J18">
         <v>1418.18</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>1525.4794988000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2022</v>
       </c>
@@ -15869,7 +16287,7 @@
         <v>1274.19</v>
       </c>
       <c r="C19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.10706367679709121</v>
       </c>
       <c r="E19" t="s">
@@ -15885,8 +16303,12 @@
       <c r="J19">
         <v>1274.19</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>1370.5952154000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E20" t="s">
         <v>98</v>
       </c>
@@ -15901,8 +16323,12 @@
         <f>$F$26*J19</f>
         <v>1223.0826720057416</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>1315.621106969696</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E21" t="s">
         <v>99</v>
       </c>
@@ -15914,38 +16340,54 @@
         <v>2024</v>
       </c>
       <c r="J21">
-        <f t="shared" ref="J21:J27" si="1">$F$26*J20</f>
+        <f t="shared" ref="J21:J37" si="2">$F$26*J20</f>
         <v>1174.0252415736306</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>1262.8519913510916</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I22">
         <v>2025</v>
       </c>
       <c r="J22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1126.9354880089018</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>1212.1994270316554</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I23">
         <v>2026</v>
       </c>
       <c r="J23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1081.7344884609217</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>1163.5785198578751</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I24">
         <v>2027</v>
       </c>
       <c r="J24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1038.3464856477826</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>1116.9077807518938</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E25" t="s">
         <v>100</v>
       </c>
@@ -15957,11 +16399,15 @@
         <v>2028</v>
       </c>
       <c r="J25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>996.69876088641524</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>1072.1089891350814</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E26" t="s">
         <v>98</v>
       </c>
@@ -15973,11 +16419,15 @@
         <v>2029</v>
       </c>
       <c r="J26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>956.72151221542197</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>1029.1070618296408</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E27" t="s">
         <v>99</v>
       </c>
@@ -15989,8 +16439,142 @@
         <v>2030</v>
       </c>
       <c r="J27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>918.34773740636172</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>987.82992721852713</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I28">
+        <v>2031</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="2"/>
+        <v>881.51312166741229</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>948.20840445276872</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I29">
+        <v>2032</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="2"/>
+        <v>846.15592985120043</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>910.17608750374234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I30">
+        <v>2033</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="2"/>
+        <v>812.21690298613953</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>873.66923386607084</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <v>2034</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="2"/>
+        <v>779.6391589578601</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>838.62665772461185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I32">
+        <v>2035</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="2"/>
+        <v>748.36809717427434</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>804.98962740647994</v>
+      </c>
+    </row>
+    <row r="33" spans="9:11" x14ac:dyDescent="0.2">
+      <c r="I33">
+        <v>2036</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="2"/>
+        <v>718.35130705449262</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>772.70176694623558</v>
+      </c>
+    </row>
+    <row r="34" spans="9:11" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <v>2037</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="2"/>
+        <v>689.53848018821827</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>741.70896159925894</v>
+      </c>
+    </row>
+    <row r="35" spans="9:11" x14ac:dyDescent="0.2">
+      <c r="I35">
+        <v>2038</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="2"/>
+        <v>661.88132601839925</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>711.95926714495135</v>
+      </c>
+    </row>
+    <row r="36" spans="9:11" x14ac:dyDescent="0.2">
+      <c r="I36">
+        <v>2039</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="2"/>
+        <v>635.33349090582033</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>683.40282282775468</v>
+      </c>
+    </row>
+    <row r="37" spans="9:11" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <v>2040</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="2"/>
+        <v>609.85048043998643</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="0"/>
+        <v>655.99176779007587</v>
       </c>
     </row>
   </sheetData>
